--- a/extenbooks/S803_extenbook.xlsx
+++ b/extenbooks/S803_extenbook.xlsx
@@ -3197,7 +3197,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -4494,11 +4494,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4521,76 +4521,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Rate of Profit on Equity vs CR8, Bain 42-Industry Sample 1936-40</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S803_research.json", "adequacy_report": "Technical/docs/chapters/CH8_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S803_DPR.md", "epr": "Technical/docs/series/S803_EPR.md", "loader": "Technical/code/L01_loaders/L01_S803_load.py", "processor": "Technical/code/P02_processors/P02_S803_construct.py", "validator": "Technical/code/V03_validators/V03_S803_validate.py", "processed": "Technical/data/processed/S803.parquet", "chopped_csv": "Technical/chopped/S803.csv", "extenbook_xlsx": "Technical/extenbooks/S803_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-19T00:22:18.990557+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S803_extenbook.xlsx
+++ b/extenbooks/S803_extenbook.xlsx
@@ -3211,7 +3211,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-ch8-fanout</t>
+          <t>**Author**: Anu automated extraction pipeline</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3327,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Per the playbook recipe (cross_sectional): tolerance 0.5%, no splice, extension N/A.</t>
+          <t>Per the project's cross-sectional handling convention: tolerance 0.5%, no splice, extension N/A.</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5. **R² values from Shaikh's text** (0.0781 linear, 0.1896 quadratic, 0.033 grouped corrected) are reported in the EPR provenance and can be re-computed from the loaded data for sanity-check in A05 analysis if desired (not required by playbook).</t>
+          <t>5. **R² values from Shaikh's text** (0.0781 linear, 0.1896 quadratic, 0.033 grouped corrected) are reported in the EPR provenance and can be re-computed from the loaded data for sanity-check in downstream analysis if desired (not required by the extraction convention).</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3778,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>- **Tolerance**: ±0.5% (cross_sectional per playbook).</t>
+          <t>- **Tolerance**: ±0.5% (cross-sectional convention).</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-ch8-fanout</t>
+          <t>**Author**: Anu automated extraction pipeline</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Per the playbook recipe (cross_sectional):</t>
+          <t>Per the project's cross-sectional handling convention:</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-19T00:09:40.830627+00:00</t>
+          <t>2026-07-02T06:25:42.182165+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S803_extenbook.xlsx
+++ b/extenbooks/S803_extenbook.xlsx
@@ -4479,7 +4479,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:25:42.182165+00:00</t>
+          <t>2026-07-11T03:44:26.341987+00:00</t>
         </is>
       </c>
     </row>
@@ -4494,11 +4494,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4521,6 +4521,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BAIN_1951_QJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful reconstruction of Shaikh Figures 8.3 and 8.4 (Ch8, pp.374-375) from Bain (1951, QJE) with Demsetz (1973b) corrections: rate of profit on equity (ROE) versus eight-firm concentration ratio (CR8) for 42 US manufacturing industries averaged over 1936-1940 (Fig 8.3 scatter) and the same data grouped by CR8 decile (Fig 8.4). Construction-relevant: Shaikh's centerpiece exhibit that even Bain's own data show no robust positive concentration-profit correlation (beta=0.0521, R^2=0.0781 scatter; R^2=0.033 corrected grouped). COVERAGE_SHORT/COVERAGE_START prescreen flags are STALE FALSE POSITIVES: this is an index-axis cross-section in which year=1938 is a constant placeholder (midpoint of Bain's 1936-40 averaging window); the genuine axes are CR8/ROE (Fig 8.3) and decile/CR8-midpoint (Fig 8.4). There is no time coverage gap to investigate.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S803_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S803_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Combines Bain 1951 Tables I &amp; II plus Demsetz 1973b corrections; 104 rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cross_sectional</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
